--- a/config_guide.xlsx
+++ b/config_guide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pgone-my.sharepoint.com/personal/zhang_s_37_pg_com/Documents/Documents/GitHub/chainsight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="969" documentId="11_07ABF5C91929F43ECF01C79A62C7FF872126F2EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28BD33BB-18BE-4460-B702-085370DBB6FD}"/>
+  <xr:revisionPtr revIDLastSave="1082" documentId="11_07ABF5C91929F43ECF01C79A62C7FF872126F2EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7760530E-AAB4-472A-A849-6E10E032E84E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="771" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="771" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SIT Design" sheetId="26" r:id="rId1"/>
@@ -769,7 +769,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -905,8 +905,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -919,6 +919,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1207,19 +1211,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFCB1DA0-9536-47EC-930C-33A86D3FFCFD}">
   <dimension ref="B3:I25"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="36.28515625" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" customWidth="1"/>
-    <col min="8" max="8" width="22.140625" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="6" max="6" width="36.33203125" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" customWidth="1"/>
+    <col min="8" max="8" width="22.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1245,7 +1249,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
@@ -1271,7 +1275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
@@ -1291,17 +1295,17 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
@@ -1315,7 +1319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="28.9">
+    <row r="16" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>26</v>
       </c>
@@ -1329,7 +1333,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="6">
         <v>4.2</v>
       </c>
@@ -1343,7 +1347,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="6">
         <v>6.8</v>
       </c>
@@ -1357,7 +1361,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="6">
         <v>7.6</v>
       </c>
@@ -1371,7 +1375,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="6">
         <v>9.6</v>
       </c>
@@ -1385,7 +1389,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="6">
         <v>12.5</v>
       </c>
@@ -1399,7 +1403,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="6">
         <v>13.5</v>
       </c>
@@ -1413,7 +1417,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="6">
         <v>14.6</v>
       </c>
@@ -1427,7 +1431,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="6">
         <v>16.5</v>
       </c>
@@ -1441,7 +1445,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="25" spans="2:5">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="6">
         <v>17.5</v>
       </c>
@@ -1466,15 +1470,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -1488,7 +1492,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -1502,7 +1506,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>162</v>
       </c>
@@ -1516,7 +1520,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>169</v>
       </c>
@@ -1530,7 +1534,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>162</v>
       </c>
@@ -1544,7 +1548,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -1558,7 +1562,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>169</v>
       </c>
@@ -1583,13 +1587,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:B537"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
@@ -1597,7 +1601,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>45658</v>
       </c>
@@ -1605,7 +1609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>45659</v>
       </c>
@@ -1613,7 +1617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>45660</v>
       </c>
@@ -1621,7 +1625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>45661</v>
       </c>
@@ -1629,7 +1633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>45662</v>
       </c>
@@ -1637,7 +1641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>45663</v>
       </c>
@@ -1645,7 +1649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>45664</v>
       </c>
@@ -1653,7 +1657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>45665</v>
       </c>
@@ -1661,7 +1665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>45666</v>
       </c>
@@ -1669,7 +1673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
         <v>45667</v>
       </c>
@@ -1677,7 +1681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
         <v>45668</v>
       </c>
@@ -1685,7 +1689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="12">
         <v>45669</v>
       </c>
@@ -1693,7 +1697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
         <v>45670</v>
       </c>
@@ -1701,7 +1705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="12">
         <v>45671</v>
       </c>
@@ -1709,7 +1713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
         <v>45672</v>
       </c>
@@ -1717,7 +1721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="12">
         <v>45673</v>
       </c>
@@ -1725,7 +1729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="12">
         <v>45674</v>
       </c>
@@ -1733,7 +1737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="12">
         <v>45675</v>
       </c>
@@ -1741,7 +1745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="12">
         <v>45676</v>
       </c>
@@ -1749,7 +1753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="12">
         <v>45677</v>
       </c>
@@ -1757,7 +1761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="12">
         <v>45678</v>
       </c>
@@ -1765,7 +1769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="12">
         <v>45679</v>
       </c>
@@ -1773,7 +1777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="12">
         <v>45680</v>
       </c>
@@ -1781,7 +1785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="12">
         <v>45681</v>
       </c>
@@ -1789,7 +1793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="12">
         <v>45682</v>
       </c>
@@ -1797,7 +1801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="12">
         <v>45683</v>
       </c>
@@ -1805,7 +1809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="12">
         <v>45684</v>
       </c>
@@ -1813,7 +1817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="12">
         <v>45685</v>
       </c>
@@ -1821,7 +1825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="12">
         <v>45686</v>
       </c>
@@ -1829,7 +1833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="12">
         <v>45687</v>
       </c>
@@ -1837,7 +1841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="12">
         <v>45688</v>
       </c>
@@ -1845,7 +1849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="12">
         <v>45689</v>
       </c>
@@ -1853,7 +1857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
         <v>45690</v>
       </c>
@@ -1861,7 +1865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="12">
         <v>45691</v>
       </c>
@@ -1869,7 +1873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="12">
         <v>45692</v>
       </c>
@@ -1877,7 +1881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="12">
         <v>45693</v>
       </c>
@@ -1885,7 +1889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="12">
         <v>45694</v>
       </c>
@@ -1893,7 +1897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="12">
         <v>45695</v>
       </c>
@@ -1901,7 +1905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="12">
         <v>45696</v>
       </c>
@@ -1909,7 +1913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="12">
         <v>45697</v>
       </c>
@@ -1917,7 +1921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="12">
         <v>45698</v>
       </c>
@@ -1925,7 +1929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="12">
         <v>45699</v>
       </c>
@@ -1933,7 +1937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="12">
         <v>45700</v>
       </c>
@@ -1941,7 +1945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="12">
         <v>45701</v>
       </c>
@@ -1949,7 +1953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
         <v>45702</v>
       </c>
@@ -1957,7 +1961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="12">
         <v>45703</v>
       </c>
@@ -1965,7 +1969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="12">
         <v>45704</v>
       </c>
@@ -1973,7 +1977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="12">
         <v>45705</v>
       </c>
@@ -1981,7 +1985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="12">
         <v>45706</v>
       </c>
@@ -1989,7 +1993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="12">
         <v>45707</v>
       </c>
@@ -1997,7 +2001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="12">
         <v>45708</v>
       </c>
@@ -2005,7 +2009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="12">
         <v>45709</v>
       </c>
@@ -2013,7 +2017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="12">
         <v>45710</v>
       </c>
@@ -2021,7 +2025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="12">
         <v>45711</v>
       </c>
@@ -2029,7 +2033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="12">
         <v>45712</v>
       </c>
@@ -2037,7 +2041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="12">
         <v>45713</v>
       </c>
@@ -2045,7 +2049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="12">
         <v>45714</v>
       </c>
@@ -2053,7 +2057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
         <v>45715</v>
       </c>
@@ -2061,7 +2065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="12">
         <v>45716</v>
       </c>
@@ -2069,7 +2073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="12">
         <v>45717</v>
       </c>
@@ -2077,7 +2081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="12">
         <v>45718</v>
       </c>
@@ -2085,7 +2089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="12">
         <v>45719</v>
       </c>
@@ -2093,7 +2097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="12">
         <v>45720</v>
       </c>
@@ -2101,7 +2105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="12">
         <v>45721</v>
       </c>
@@ -2109,7 +2113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="12">
         <v>45722</v>
       </c>
@@ -2117,7 +2121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="12">
         <v>45723</v>
       </c>
@@ -2125,7 +2129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="12">
         <v>45724</v>
       </c>
@@ -2133,7 +2137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="12">
         <v>45725</v>
       </c>
@@ -2141,7 +2145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="12">
         <v>45726</v>
       </c>
@@ -2149,7 +2153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
         <v>45727</v>
       </c>
@@ -2157,7 +2161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="12">
         <v>45728</v>
       </c>
@@ -2165,7 +2169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="12">
         <v>45729</v>
       </c>
@@ -2173,7 +2177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="12">
         <v>45730</v>
       </c>
@@ -2181,7 +2185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="12">
         <v>45731</v>
       </c>
@@ -2189,7 +2193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="12">
         <v>45732</v>
       </c>
@@ -2197,7 +2201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="12">
         <v>45733</v>
       </c>
@@ -2205,7 +2209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="12">
         <v>45734</v>
       </c>
@@ -2213,7 +2217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="12">
         <v>45735</v>
       </c>
@@ -2221,7 +2225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="12">
         <v>45736</v>
       </c>
@@ -2229,7 +2233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="12">
         <v>45737</v>
       </c>
@@ -2237,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="12">
         <v>45738</v>
       </c>
@@ -2245,7 +2249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="12">
         <v>45739</v>
       </c>
@@ -2253,7 +2257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="12">
         <v>45740</v>
       </c>
@@ -2261,7 +2265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="12">
         <v>45741</v>
       </c>
@@ -2269,7 +2273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="12">
         <v>45742</v>
       </c>
@@ -2277,7 +2281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="12">
         <v>45743</v>
       </c>
@@ -2285,7 +2289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="12">
         <v>45744</v>
       </c>
@@ -2293,7 +2297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="12">
         <v>45745</v>
       </c>
@@ -2301,7 +2305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="12">
         <v>45746</v>
       </c>
@@ -2309,7 +2313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="12">
         <v>45747</v>
       </c>
@@ -2317,7 +2321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="12">
         <v>45748</v>
       </c>
@@ -2325,7 +2329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="12">
         <v>45749</v>
       </c>
@@ -2333,7 +2337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="12">
         <v>45750</v>
       </c>
@@ -2341,7 +2345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="12">
         <v>45751</v>
       </c>
@@ -2349,7 +2353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="12">
         <v>45752</v>
       </c>
@@ -2357,7 +2361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="12">
         <v>45753</v>
       </c>
@@ -2365,7 +2369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="12">
         <v>45754</v>
       </c>
@@ -2373,7 +2377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="12">
         <v>45755</v>
       </c>
@@ -2381,7 +2385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="12">
         <v>45756</v>
       </c>
@@ -2389,7 +2393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="12">
         <v>45757</v>
       </c>
@@ -2397,7 +2401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="12">
         <v>45758</v>
       </c>
@@ -2405,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="12">
         <v>45759</v>
       </c>
@@ -2413,7 +2417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="12">
         <v>45760</v>
       </c>
@@ -2421,7 +2425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="12">
         <v>45761</v>
       </c>
@@ -2429,7 +2433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="12">
         <v>45762</v>
       </c>
@@ -2437,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="12">
         <v>45763</v>
       </c>
@@ -2445,7 +2449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="12">
         <v>45764</v>
       </c>
@@ -2453,7 +2457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="12">
         <v>45765</v>
       </c>
@@ -2461,7 +2465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="12">
         <v>45766</v>
       </c>
@@ -2469,7 +2473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="12">
         <v>45767</v>
       </c>
@@ -2477,7 +2481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="12">
         <v>45768</v>
       </c>
@@ -2485,7 +2489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="12">
         <v>45769</v>
       </c>
@@ -2493,7 +2497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="12">
         <v>45770</v>
       </c>
@@ -2501,7 +2505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="12">
         <v>45771</v>
       </c>
@@ -2509,7 +2513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="12">
         <v>45772</v>
       </c>
@@ -2517,7 +2521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="12">
         <v>45773</v>
       </c>
@@ -2525,7 +2529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="12">
         <v>45774</v>
       </c>
@@ -2533,7 +2537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="12">
         <v>45775</v>
       </c>
@@ -2541,7 +2545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="12">
         <v>45776</v>
       </c>
@@ -2549,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="12">
         <v>45777</v>
       </c>
@@ -2557,7 +2561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="12">
         <v>45778</v>
       </c>
@@ -2565,7 +2569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="12">
         <v>45779</v>
       </c>
@@ -2573,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="12">
         <v>45780</v>
       </c>
@@ -2581,7 +2585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="12">
         <v>45781</v>
       </c>
@@ -2589,7 +2593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="12">
         <v>45782</v>
       </c>
@@ -2597,7 +2601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="12">
         <v>45783</v>
       </c>
@@ -2605,7 +2609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="12">
         <v>45784</v>
       </c>
@@ -2613,7 +2617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="12">
         <v>45785</v>
       </c>
@@ -2621,7 +2625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="12">
         <v>45786</v>
       </c>
@@ -2629,7 +2633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="12">
         <v>45787</v>
       </c>
@@ -2637,7 +2641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="12">
         <v>45788</v>
       </c>
@@ -2645,7 +2649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="12">
         <v>45789</v>
       </c>
@@ -2653,7 +2657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="12">
         <v>45790</v>
       </c>
@@ -2661,7 +2665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="12">
         <v>45791</v>
       </c>
@@ -2669,7 +2673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="12">
         <v>45792</v>
       </c>
@@ -2677,7 +2681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="12">
         <v>45793</v>
       </c>
@@ -2685,7 +2689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="12">
         <v>45794</v>
       </c>
@@ -2693,7 +2697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="12">
         <v>45795</v>
       </c>
@@ -2701,7 +2705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="12">
         <v>45796</v>
       </c>
@@ -2709,7 +2713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="12">
         <v>45797</v>
       </c>
@@ -2717,7 +2721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="12">
         <v>45798</v>
       </c>
@@ -2725,7 +2729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="12">
         <v>45799</v>
       </c>
@@ -2733,7 +2737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="12">
         <v>45800</v>
       </c>
@@ -2741,7 +2745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="12">
         <v>45801</v>
       </c>
@@ -2749,7 +2753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="12">
         <v>45802</v>
       </c>
@@ -2757,7 +2761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="12">
         <v>45803</v>
       </c>
@@ -2765,7 +2769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="12">
         <v>45804</v>
       </c>
@@ -2773,7 +2777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="12">
         <v>45805</v>
       </c>
@@ -2781,7 +2785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="12">
         <v>45806</v>
       </c>
@@ -2789,7 +2793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="12">
         <v>45807</v>
       </c>
@@ -2797,7 +2801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="12">
         <v>45808</v>
       </c>
@@ -2805,7 +2809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="12">
         <v>45809</v>
       </c>
@@ -2813,7 +2817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="12">
         <v>45810</v>
       </c>
@@ -2821,7 +2825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="12">
         <v>45811</v>
       </c>
@@ -2829,7 +2833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="12">
         <v>45812</v>
       </c>
@@ -2837,7 +2841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="12">
         <v>45813</v>
       </c>
@@ -2845,7 +2849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="12">
         <v>45814</v>
       </c>
@@ -2853,7 +2857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="12">
         <v>45815</v>
       </c>
@@ -2861,7 +2865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="12">
         <v>45816</v>
       </c>
@@ -2869,7 +2873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="12">
         <v>45817</v>
       </c>
@@ -2877,7 +2881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="12">
         <v>45818</v>
       </c>
@@ -2885,7 +2889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="12">
         <v>45819</v>
       </c>
@@ -2893,7 +2897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="12">
         <v>45820</v>
       </c>
@@ -2901,7 +2905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="12">
         <v>45821</v>
       </c>
@@ -2909,7 +2913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="12">
         <v>45822</v>
       </c>
@@ -2917,7 +2921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="12">
         <v>45823</v>
       </c>
@@ -2925,7 +2929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="12">
         <v>45824</v>
       </c>
@@ -2933,7 +2937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="12">
         <v>45825</v>
       </c>
@@ -2941,7 +2945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="12">
         <v>45826</v>
       </c>
@@ -2949,7 +2953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="12">
         <v>45827</v>
       </c>
@@ -2957,7 +2961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="12">
         <v>45828</v>
       </c>
@@ -2965,7 +2969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="12">
         <v>45829</v>
       </c>
@@ -2973,7 +2977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="12">
         <v>45830</v>
       </c>
@@ -2981,7 +2985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="12">
         <v>45831</v>
       </c>
@@ -2989,7 +2993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="12">
         <v>45832</v>
       </c>
@@ -2997,7 +3001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="12">
         <v>45833</v>
       </c>
@@ -3005,7 +3009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="12">
         <v>45834</v>
       </c>
@@ -3013,7 +3017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="12">
         <v>45835</v>
       </c>
@@ -3021,7 +3025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="12">
         <v>45836</v>
       </c>
@@ -3029,7 +3033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="12">
         <v>45837</v>
       </c>
@@ -3037,7 +3041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="12">
         <v>45838</v>
       </c>
@@ -3045,7 +3049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="12">
         <v>45839</v>
       </c>
@@ -3053,7 +3057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="12">
         <v>45840</v>
       </c>
@@ -3061,7 +3065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="12">
         <v>45841</v>
       </c>
@@ -3069,7 +3073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="12">
         <v>45842</v>
       </c>
@@ -3077,7 +3081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="12">
         <v>45843</v>
       </c>
@@ -3085,7 +3089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="12">
         <v>45844</v>
       </c>
@@ -3093,7 +3097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="12">
         <v>45845</v>
       </c>
@@ -3101,7 +3105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="12">
         <v>45846</v>
       </c>
@@ -3109,7 +3113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="12">
         <v>45847</v>
       </c>
@@ -3117,7 +3121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="12">
         <v>45848</v>
       </c>
@@ -3125,7 +3129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="12">
         <v>45849</v>
       </c>
@@ -3133,7 +3137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="12">
         <v>45850</v>
       </c>
@@ -3141,7 +3145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="12">
         <v>45851</v>
       </c>
@@ -3149,7 +3153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="12">
         <v>45852</v>
       </c>
@@ -3157,7 +3161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="12">
         <v>45853</v>
       </c>
@@ -3165,7 +3169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="12">
         <v>45854</v>
       </c>
@@ -3173,7 +3177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="12">
         <v>45855</v>
       </c>
@@ -3181,7 +3185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="12">
         <v>45856</v>
       </c>
@@ -3189,7 +3193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="12">
         <v>45857</v>
       </c>
@@ -3197,7 +3201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="12">
         <v>45858</v>
       </c>
@@ -3205,7 +3209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="12">
         <v>45859</v>
       </c>
@@ -3213,7 +3217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="12">
         <v>45860</v>
       </c>
@@ -3221,7 +3225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="12">
         <v>45861</v>
       </c>
@@ -3229,7 +3233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="12">
         <v>45862</v>
       </c>
@@ -3237,7 +3241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="12">
         <v>45863</v>
       </c>
@@ -3245,7 +3249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="12">
         <v>45864</v>
       </c>
@@ -3253,7 +3257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="12">
         <v>45865</v>
       </c>
@@ -3261,7 +3265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="12">
         <v>45866</v>
       </c>
@@ -3269,7 +3273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="12">
         <v>45867</v>
       </c>
@@ -3277,7 +3281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="12">
         <v>45868</v>
       </c>
@@ -3285,7 +3289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="12">
         <v>45869</v>
       </c>
@@ -3293,7 +3297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="12">
         <v>45870</v>
       </c>
@@ -3301,7 +3305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="12">
         <v>45871</v>
       </c>
@@ -3309,7 +3313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:2">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="12">
         <v>45872</v>
       </c>
@@ -3317,7 +3321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="12">
         <v>45873</v>
       </c>
@@ -3325,7 +3329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="12">
         <v>45874</v>
       </c>
@@ -3333,7 +3337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="12">
         <v>45875</v>
       </c>
@@ -3341,7 +3345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:2">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="12">
         <v>45876</v>
       </c>
@@ -3349,7 +3353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="12">
         <v>45877</v>
       </c>
@@ -3357,7 +3361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="12">
         <v>45878</v>
       </c>
@@ -3365,7 +3369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="12">
         <v>45879</v>
       </c>
@@ -3373,7 +3377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="12">
         <v>45880</v>
       </c>
@@ -3381,7 +3385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="12">
         <v>45881</v>
       </c>
@@ -3389,7 +3393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="12">
         <v>45882</v>
       </c>
@@ -3397,7 +3401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="12">
         <v>45883</v>
       </c>
@@ -3405,7 +3409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="12">
         <v>45884</v>
       </c>
@@ -3413,7 +3417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="12">
         <v>45885</v>
       </c>
@@ -3421,7 +3425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="12">
         <v>45886</v>
       </c>
@@ -3429,7 +3433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="12">
         <v>45887</v>
       </c>
@@ -3437,7 +3441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="12">
         <v>45888</v>
       </c>
@@ -3445,7 +3449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="12">
         <v>45889</v>
       </c>
@@ -3453,7 +3457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:2">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="12">
         <v>45890</v>
       </c>
@@ -3461,7 +3465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="12">
         <v>45891</v>
       </c>
@@ -3469,7 +3473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="12">
         <v>45892</v>
       </c>
@@ -3477,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="12">
         <v>45893</v>
       </c>
@@ -3485,7 +3489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="12">
         <v>45894</v>
       </c>
@@ -3493,7 +3497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="12">
         <v>45895</v>
       </c>
@@ -3501,7 +3505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="12">
         <v>45896</v>
       </c>
@@ -3509,7 +3513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="12">
         <v>45897</v>
       </c>
@@ -3517,7 +3521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="12">
         <v>45898</v>
       </c>
@@ -3525,7 +3529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:2">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="12">
         <v>45899</v>
       </c>
@@ -3533,7 +3537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="12">
         <v>45900</v>
       </c>
@@ -3541,7 +3545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="12">
         <v>45901</v>
       </c>
@@ -3549,7 +3553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="12">
         <v>45902</v>
       </c>
@@ -3557,7 +3561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="12">
         <v>45903</v>
       </c>
@@ -3565,7 +3569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="12">
         <v>45904</v>
       </c>
@@ -3573,7 +3577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="12">
         <v>45905</v>
       </c>
@@ -3581,7 +3585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="12">
         <v>45906</v>
       </c>
@@ -3589,7 +3593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="12">
         <v>45907</v>
       </c>
@@ -3597,7 +3601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="12">
         <v>45908</v>
       </c>
@@ -3605,7 +3609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="12">
         <v>45909</v>
       </c>
@@ -3613,7 +3617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="12">
         <v>45910</v>
       </c>
@@ -3621,7 +3625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="12">
         <v>45911</v>
       </c>
@@ -3629,7 +3633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="12">
         <v>45912</v>
       </c>
@@ -3637,7 +3641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="12">
         <v>45913</v>
       </c>
@@ -3645,7 +3649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:2">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="12">
         <v>45914</v>
       </c>
@@ -3653,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="12">
         <v>45915</v>
       </c>
@@ -3661,7 +3665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="12">
         <v>45916</v>
       </c>
@@ -3669,7 +3673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="12">
         <v>45917</v>
       </c>
@@ -3677,7 +3681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:2">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="12">
         <v>45918</v>
       </c>
@@ -3685,7 +3689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="12">
         <v>45919</v>
       </c>
@@ -3693,7 +3697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="12">
         <v>45920</v>
       </c>
@@ -3701,7 +3705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="12">
         <v>45921</v>
       </c>
@@ -3709,7 +3713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:2">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="12">
         <v>45922</v>
       </c>
@@ -3717,7 +3721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:2">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="12">
         <v>45923</v>
       </c>
@@ -3725,7 +3729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:2">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="12">
         <v>45924</v>
       </c>
@@ -3733,7 +3737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:2">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="12">
         <v>45925</v>
       </c>
@@ -3741,7 +3745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:2">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="12">
         <v>45926</v>
       </c>
@@ -3749,7 +3753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:2">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="12">
         <v>45927</v>
       </c>
@@ -3757,7 +3761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:2">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="12">
         <v>45928</v>
       </c>
@@ -3765,7 +3769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:2">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="12">
         <v>45929</v>
       </c>
@@ -3773,7 +3777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:2">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="12">
         <v>45930</v>
       </c>
@@ -3781,7 +3785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:2">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="12">
         <v>45931</v>
       </c>
@@ -3789,7 +3793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:2">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="12">
         <v>45932</v>
       </c>
@@ -3797,7 +3801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:2">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" s="12">
         <v>45933</v>
       </c>
@@ -3805,7 +3809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="12">
         <v>45934</v>
       </c>
@@ -3813,7 +3817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:2">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="12">
         <v>45935</v>
       </c>
@@ -3821,7 +3825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:2">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="12">
         <v>45936</v>
       </c>
@@ -3829,7 +3833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:2">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="12">
         <v>45937</v>
       </c>
@@ -3837,7 +3841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:2">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="12">
         <v>45938</v>
       </c>
@@ -3845,7 +3849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="12">
         <v>45939</v>
       </c>
@@ -3853,7 +3857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="12">
         <v>45940</v>
       </c>
@@ -3861,7 +3865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:2">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="12">
         <v>45941</v>
       </c>
@@ -3869,7 +3873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="12">
         <v>45942</v>
       </c>
@@ -3877,7 +3881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:2">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="12">
         <v>45943</v>
       </c>
@@ -3885,7 +3889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:2">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="12">
         <v>45944</v>
       </c>
@@ -3893,7 +3897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="12">
         <v>45945</v>
       </c>
@@ -3901,7 +3905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="12">
         <v>45946</v>
       </c>
@@ -3909,7 +3913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="12">
         <v>45947</v>
       </c>
@@ -3917,7 +3921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="12">
         <v>45948</v>
       </c>
@@ -3925,7 +3929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:2">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="12">
         <v>45949</v>
       </c>
@@ -3933,7 +3937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:2">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="12">
         <v>45950</v>
       </c>
@@ -3941,7 +3945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:2">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="12">
         <v>45951</v>
       </c>
@@ -3949,7 +3953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="12">
         <v>45952</v>
       </c>
@@ -3957,7 +3961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="12">
         <v>45953</v>
       </c>
@@ -3965,7 +3969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:2">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="12">
         <v>45954</v>
       </c>
@@ -3973,7 +3977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="12">
         <v>45955</v>
       </c>
@@ -3981,7 +3985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:2">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="12">
         <v>45956</v>
       </c>
@@ -3989,7 +3993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:2">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="12">
         <v>45957</v>
       </c>
@@ -3997,7 +4001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:2">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="12">
         <v>45958</v>
       </c>
@@ -4005,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:2">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="12">
         <v>45959</v>
       </c>
@@ -4013,7 +4017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:2">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="12">
         <v>45960</v>
       </c>
@@ -4021,7 +4025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="12">
         <v>45961</v>
       </c>
@@ -4029,7 +4033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:2">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="12">
         <v>45962</v>
       </c>
@@ -4037,7 +4041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:2">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="12">
         <v>45963</v>
       </c>
@@ -4045,7 +4049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:2">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="12">
         <v>45964</v>
       </c>
@@ -4053,7 +4057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:2">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="12">
         <v>45965</v>
       </c>
@@ -4061,7 +4065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="12">
         <v>45966</v>
       </c>
@@ -4069,7 +4073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:2">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="12">
         <v>45967</v>
       </c>
@@ -4077,7 +4081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:2">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="12">
         <v>45968</v>
       </c>
@@ -4085,7 +4089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:2">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" s="12">
         <v>45969</v>
       </c>
@@ -4093,7 +4097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:2">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="12">
         <v>45970</v>
       </c>
@@ -4101,7 +4105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:2">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="12">
         <v>45971</v>
       </c>
@@ -4109,7 +4113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:2">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" s="12">
         <v>45972</v>
       </c>
@@ -4117,7 +4121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:2">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="12">
         <v>45973</v>
       </c>
@@ -4125,7 +4129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:2">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="12">
         <v>45974</v>
       </c>
@@ -4133,7 +4137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="12">
         <v>45975</v>
       </c>
@@ -4141,7 +4145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="12">
         <v>45976</v>
       </c>
@@ -4149,7 +4153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:2">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="12">
         <v>45977</v>
       </c>
@@ -4157,7 +4161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:2">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="12">
         <v>45978</v>
       </c>
@@ -4165,7 +4169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:2">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="12">
         <v>45979</v>
       </c>
@@ -4173,7 +4177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:2">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="12">
         <v>45980</v>
       </c>
@@ -4181,7 +4185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:2">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="12">
         <v>45981</v>
       </c>
@@ -4189,7 +4193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:2">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="12">
         <v>45982</v>
       </c>
@@ -4197,7 +4201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:2">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="12">
         <v>45983</v>
       </c>
@@ -4205,7 +4209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:2">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="12">
         <v>45984</v>
       </c>
@@ -4213,7 +4217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:2">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="12">
         <v>45985</v>
       </c>
@@ -4221,7 +4225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:2">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="12">
         <v>45986</v>
       </c>
@@ -4229,7 +4233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:2">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="12">
         <v>45987</v>
       </c>
@@ -4237,7 +4241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:2">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" s="12">
         <v>45988</v>
       </c>
@@ -4245,7 +4249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:2">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" s="12">
         <v>45989</v>
       </c>
@@ -4253,7 +4257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:2">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" s="12">
         <v>45990</v>
       </c>
@@ -4261,7 +4265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:2">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" s="12">
         <v>45991</v>
       </c>
@@ -4269,7 +4273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:2">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" s="12">
         <v>45992</v>
       </c>
@@ -4277,7 +4281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:2">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="12">
         <v>45993</v>
       </c>
@@ -4285,7 +4289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:2">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" s="12">
         <v>45994</v>
       </c>
@@ -4293,7 +4297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:2">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" s="12">
         <v>45995</v>
       </c>
@@ -4301,7 +4305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:2">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" s="12">
         <v>45996</v>
       </c>
@@ -4309,7 +4313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:2">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" s="12">
         <v>45997</v>
       </c>
@@ -4317,7 +4321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:2">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" s="12">
         <v>45998</v>
       </c>
@@ -4325,7 +4329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:2">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" s="12">
         <v>45999</v>
       </c>
@@ -4333,7 +4337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:2">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" s="12">
         <v>46000</v>
       </c>
@@ -4341,7 +4345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:2">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" s="12">
         <v>46001</v>
       </c>
@@ -4349,7 +4353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:2">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" s="12">
         <v>46002</v>
       </c>
@@ -4357,7 +4361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:2">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" s="12">
         <v>46003</v>
       </c>
@@ -4365,7 +4369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:2">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" s="12">
         <v>46004</v>
       </c>
@@ -4373,7 +4377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:2">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" s="12">
         <v>46005</v>
       </c>
@@ -4381,7 +4385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:2">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" s="12">
         <v>46006</v>
       </c>
@@ -4389,7 +4393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:2">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" s="12">
         <v>46007</v>
       </c>
@@ -4397,7 +4401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:2">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" s="12">
         <v>46008</v>
       </c>
@@ -4405,7 +4409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:2">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" s="12">
         <v>46009</v>
       </c>
@@ -4413,7 +4417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:2">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" s="12">
         <v>46010</v>
       </c>
@@ -4421,7 +4425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:2">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" s="12">
         <v>46011</v>
       </c>
@@ -4429,7 +4433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:2">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" s="12">
         <v>46012</v>
       </c>
@@ -4437,7 +4441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:2">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" s="12">
         <v>46013</v>
       </c>
@@ -4445,7 +4449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" s="12">
         <v>46014</v>
       </c>
@@ -4453,7 +4457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:2">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" s="12">
         <v>46015</v>
       </c>
@@ -4461,7 +4465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:2">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" s="12">
         <v>46016</v>
       </c>
@@ -4469,7 +4473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" s="12">
         <v>46017</v>
       </c>
@@ -4477,7 +4481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:2">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" s="12">
         <v>46018</v>
       </c>
@@ -4485,7 +4489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:2">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" s="12">
         <v>46019</v>
       </c>
@@ -4493,7 +4497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:2">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" s="12">
         <v>46020</v>
       </c>
@@ -4501,7 +4505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:2">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" s="12">
         <v>46021</v>
       </c>
@@ -4509,7 +4513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:2">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" s="12">
         <v>46022</v>
       </c>
@@ -4517,7 +4521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:2">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" s="12">
         <v>46023</v>
       </c>
@@ -4525,7 +4529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:2">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" s="12">
         <v>46024</v>
       </c>
@@ -4533,7 +4537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:2">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" s="12">
         <v>46025</v>
       </c>
@@ -4541,7 +4545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:2">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" s="12">
         <v>46026</v>
       </c>
@@ -4549,7 +4553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:2">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" s="12">
         <v>46027</v>
       </c>
@@ -4557,7 +4561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:2">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" s="12">
         <v>46028</v>
       </c>
@@ -4565,7 +4569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:2">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" s="12">
         <v>46029</v>
       </c>
@@ -4573,7 +4577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:2">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" s="12">
         <v>46030</v>
       </c>
@@ -4581,7 +4585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:2">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" s="12">
         <v>46031</v>
       </c>
@@ -4589,7 +4593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:2">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" s="12">
         <v>46032</v>
       </c>
@@ -4597,7 +4601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:2">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" s="12">
         <v>46033</v>
       </c>
@@ -4605,7 +4609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:2">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" s="12">
         <v>46034</v>
       </c>
@@ -4613,7 +4617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:2">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" s="12">
         <v>46035</v>
       </c>
@@ -4621,7 +4625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:2">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" s="12">
         <v>46036</v>
       </c>
@@ -4629,7 +4633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:2">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" s="12">
         <v>46037</v>
       </c>
@@ -4637,7 +4641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:2">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" s="12">
         <v>46038</v>
       </c>
@@ -4645,7 +4649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:2">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" s="12">
         <v>46039</v>
       </c>
@@ -4653,7 +4657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:2">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" s="12">
         <v>46040</v>
       </c>
@@ -4661,7 +4665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:2">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" s="12">
         <v>46041</v>
       </c>
@@ -4669,7 +4673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:2">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" s="12">
         <v>46042</v>
       </c>
@@ -4677,7 +4681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:2">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" s="12">
         <v>46043</v>
       </c>
@@ -4685,7 +4689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:2">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" s="12">
         <v>46044</v>
       </c>
@@ -4693,7 +4697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:2">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" s="12">
         <v>46045</v>
       </c>
@@ -4701,7 +4705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:2">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" s="12">
         <v>46046</v>
       </c>
@@ -4709,7 +4713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:2">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" s="12">
         <v>46047</v>
       </c>
@@ -4717,7 +4721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:2">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" s="12">
         <v>46048</v>
       </c>
@@ -4725,7 +4729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:2">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" s="12">
         <v>46049</v>
       </c>
@@ -4733,7 +4737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:2">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" s="12">
         <v>46050</v>
       </c>
@@ -4741,7 +4745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:2">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" s="12">
         <v>46051</v>
       </c>
@@ -4749,7 +4753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:2">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" s="12">
         <v>46052</v>
       </c>
@@ -4757,7 +4761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:2">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" s="12">
         <v>46053</v>
       </c>
@@ -4765,7 +4769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:2">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" s="12">
         <v>46054</v>
       </c>
@@ -4773,7 +4777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:2">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" s="12">
         <v>46055</v>
       </c>
@@ -4781,7 +4785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:2">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" s="12">
         <v>46056</v>
       </c>
@@ -4789,7 +4793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:2">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" s="12">
         <v>46057</v>
       </c>
@@ -4797,7 +4801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:2">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" s="12">
         <v>46058</v>
       </c>
@@ -4805,7 +4809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:2">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" s="12">
         <v>46059</v>
       </c>
@@ -4813,7 +4817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:2">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" s="12">
         <v>46060</v>
       </c>
@@ -4821,7 +4825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:2">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" s="12">
         <v>46061</v>
       </c>
@@ -4829,7 +4833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:2">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" s="12">
         <v>46062</v>
       </c>
@@ -4837,7 +4841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:2">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" s="12">
         <v>46063</v>
       </c>
@@ -4845,7 +4849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:2">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" s="12">
         <v>46064</v>
       </c>
@@ -4853,7 +4857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:2">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" s="12">
         <v>46065</v>
       </c>
@@ -4861,7 +4865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:2">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" s="12">
         <v>46066</v>
       </c>
@@ -4869,7 +4873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:2">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" s="12">
         <v>46067</v>
       </c>
@@ -4877,7 +4881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:2">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" s="12">
         <v>46068</v>
       </c>
@@ -4885,7 +4889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:2">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" s="12">
         <v>46069</v>
       </c>
@@ -4893,7 +4897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:2">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" s="12">
         <v>46070</v>
       </c>
@@ -4901,7 +4905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:2">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" s="12">
         <v>46071</v>
       </c>
@@ -4909,7 +4913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:2">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" s="12">
         <v>46072</v>
       </c>
@@ -4917,7 +4921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:2">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" s="12">
         <v>46073</v>
       </c>
@@ -4925,7 +4929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:2">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" s="12">
         <v>46074</v>
       </c>
@@ -4933,7 +4937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:2">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" s="12">
         <v>46075</v>
       </c>
@@ -4941,7 +4945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:2">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" s="12">
         <v>46076</v>
       </c>
@@ -4949,7 +4953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:2">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" s="12">
         <v>46077</v>
       </c>
@@ -4957,7 +4961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:2">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" s="12">
         <v>46078</v>
       </c>
@@ -4965,7 +4969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:2">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" s="12">
         <v>46079</v>
       </c>
@@ -4973,7 +4977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:2">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" s="12">
         <v>46080</v>
       </c>
@@ -4981,7 +4985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:2">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" s="12">
         <v>46081</v>
       </c>
@@ -4989,7 +4993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:2">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" s="12">
         <v>46082</v>
       </c>
@@ -4997,7 +5001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:2">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" s="12">
         <v>46083</v>
       </c>
@@ -5005,7 +5009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:2">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" s="12">
         <v>46084</v>
       </c>
@@ -5013,7 +5017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:2">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" s="12">
         <v>46085</v>
       </c>
@@ -5021,7 +5025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:2">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" s="12">
         <v>46086</v>
       </c>
@@ -5029,7 +5033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:2">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" s="12">
         <v>46087</v>
       </c>
@@ -5037,7 +5041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:2">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" s="12">
         <v>46088</v>
       </c>
@@ -5045,7 +5049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:2">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" s="12">
         <v>46089</v>
       </c>
@@ -5053,7 +5057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:2">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" s="12">
         <v>46090</v>
       </c>
@@ -5061,7 +5065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:2">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" s="12">
         <v>46091</v>
       </c>
@@ -5069,7 +5073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:2">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" s="12">
         <v>46092</v>
       </c>
@@ -5077,7 +5081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:2">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" s="12">
         <v>46093</v>
       </c>
@@ -5085,7 +5089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:2">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438" s="12">
         <v>46094</v>
       </c>
@@ -5093,7 +5097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:2">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" s="12">
         <v>46095</v>
       </c>
@@ -5101,7 +5105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:2">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" s="12">
         <v>46096</v>
       </c>
@@ -5109,7 +5113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:2">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" s="12">
         <v>46097</v>
       </c>
@@ -5117,7 +5121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:2">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="12">
         <v>46098</v>
       </c>
@@ -5125,7 +5129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:2">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" s="12">
         <v>46099</v>
       </c>
@@ -5133,7 +5137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:2">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444" s="12">
         <v>46100</v>
       </c>
@@ -5141,7 +5145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:2">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" s="12">
         <v>46101</v>
       </c>
@@ -5149,7 +5153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:2">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" s="12">
         <v>46102</v>
       </c>
@@ -5157,7 +5161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:2">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" s="12">
         <v>46103</v>
       </c>
@@ -5165,7 +5169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:2">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" s="12">
         <v>46104</v>
       </c>
@@ -5173,7 +5177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:2">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" s="12">
         <v>46105</v>
       </c>
@@ -5181,7 +5185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:2">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" s="12">
         <v>46106</v>
       </c>
@@ -5189,7 +5193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:2">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" s="12">
         <v>46107</v>
       </c>
@@ -5197,7 +5201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:2">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" s="12">
         <v>46108</v>
       </c>
@@ -5205,7 +5209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:2">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" s="12">
         <v>46109</v>
       </c>
@@ -5213,7 +5217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:2">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" s="12">
         <v>46110</v>
       </c>
@@ -5221,7 +5225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:2">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455" s="12">
         <v>46111</v>
       </c>
@@ -5229,7 +5233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:2">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456" s="12">
         <v>46112</v>
       </c>
@@ -5237,7 +5241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:2">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457" s="12">
         <v>46113</v>
       </c>
@@ -5245,7 +5249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:2">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458" s="12">
         <v>46114</v>
       </c>
@@ -5253,7 +5257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:2">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459" s="12">
         <v>46115</v>
       </c>
@@ -5261,7 +5265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:2">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460" s="12">
         <v>46116</v>
       </c>
@@ -5269,7 +5273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:2">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461" s="12">
         <v>46117</v>
       </c>
@@ -5277,7 +5281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:2">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462" s="12">
         <v>46118</v>
       </c>
@@ -5285,7 +5289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:2">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463" s="12">
         <v>46119</v>
       </c>
@@ -5293,7 +5297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:2">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464" s="12">
         <v>46120</v>
       </c>
@@ -5301,7 +5305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:2">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465" s="12">
         <v>46121</v>
       </c>
@@ -5309,7 +5313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:2">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466" s="12">
         <v>46122</v>
       </c>
@@ -5317,7 +5321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:2">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467" s="12">
         <v>46123</v>
       </c>
@@ -5325,7 +5329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:2">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468" s="12">
         <v>46124</v>
       </c>
@@ -5333,7 +5337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:2">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469" s="12">
         <v>46125</v>
       </c>
@@ -5341,7 +5345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:2">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470" s="12">
         <v>46126</v>
       </c>
@@ -5349,7 +5353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:2">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471" s="12">
         <v>46127</v>
       </c>
@@ -5357,7 +5361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:2">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472" s="12">
         <v>46128</v>
       </c>
@@ -5365,7 +5369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:2">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473" s="12">
         <v>46129</v>
       </c>
@@ -5373,7 +5377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:2">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474" s="12">
         <v>46130</v>
       </c>
@@ -5381,7 +5385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:2">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475" s="12">
         <v>46131</v>
       </c>
@@ -5389,7 +5393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:2">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476" s="12">
         <v>46132</v>
       </c>
@@ -5397,7 +5401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:2">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477" s="12">
         <v>46133</v>
       </c>
@@ -5405,7 +5409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:2">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478" s="12">
         <v>46134</v>
       </c>
@@ -5413,7 +5417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:2">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479" s="12">
         <v>46135</v>
       </c>
@@ -5421,7 +5425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:2">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480" s="12">
         <v>46136</v>
       </c>
@@ -5429,7 +5433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:2">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481" s="12">
         <v>46137</v>
       </c>
@@ -5437,7 +5441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:2">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482" s="12">
         <v>46138</v>
       </c>
@@ -5445,7 +5449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:2">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483" s="12">
         <v>46139</v>
       </c>
@@ -5453,7 +5457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:2">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484" s="12">
         <v>46140</v>
       </c>
@@ -5461,7 +5465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:2">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A485" s="12">
         <v>46141</v>
       </c>
@@ -5469,7 +5473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:2">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486" s="12">
         <v>46142</v>
       </c>
@@ -5477,7 +5481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:2">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487" s="12">
         <v>46143</v>
       </c>
@@ -5485,7 +5489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:2">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488" s="12">
         <v>46144</v>
       </c>
@@ -5493,7 +5497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:2">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489" s="12">
         <v>46145</v>
       </c>
@@ -5501,7 +5505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:2">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490" s="12">
         <v>46146</v>
       </c>
@@ -5509,7 +5513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:2">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491" s="12">
         <v>46147</v>
       </c>
@@ -5517,7 +5521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:2">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492" s="12">
         <v>46148</v>
       </c>
@@ -5525,7 +5529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:2">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493" s="12">
         <v>46149</v>
       </c>
@@ -5533,7 +5537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:2">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494" s="12">
         <v>46150</v>
       </c>
@@ -5541,7 +5545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:2">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495" s="12">
         <v>46151</v>
       </c>
@@ -5549,7 +5553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:2">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A496" s="12">
         <v>46152</v>
       </c>
@@ -5557,7 +5561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:2">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497" s="12">
         <v>46153</v>
       </c>
@@ -5565,7 +5569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:2">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498" s="12">
         <v>46154</v>
       </c>
@@ -5573,7 +5577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="1:2">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499" s="12">
         <v>46155</v>
       </c>
@@ -5581,7 +5585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:2">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500" s="12">
         <v>46156</v>
       </c>
@@ -5589,7 +5593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:2">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501" s="12">
         <v>46157</v>
       </c>
@@ -5597,7 +5601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:2">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502" s="12">
         <v>46158</v>
       </c>
@@ -5605,7 +5609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:2">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503" s="12">
         <v>46159</v>
       </c>
@@ -5613,7 +5617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:2">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504" s="12">
         <v>46160</v>
       </c>
@@ -5621,7 +5625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:2">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505" s="12">
         <v>46161</v>
       </c>
@@ -5629,7 +5633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:2">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506" s="12">
         <v>46162</v>
       </c>
@@ -5637,7 +5641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:2">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507" s="12">
         <v>46163</v>
       </c>
@@ -5645,7 +5649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:2">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508" s="12">
         <v>46164</v>
       </c>
@@ -5653,7 +5657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:2">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509" s="12">
         <v>46165</v>
       </c>
@@ -5661,7 +5665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:2">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A510" s="12">
         <v>46166</v>
       </c>
@@ -5669,7 +5673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:2">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511" s="12">
         <v>46167</v>
       </c>
@@ -5677,7 +5681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:2">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512" s="12">
         <v>46168</v>
       </c>
@@ -5685,7 +5689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:2">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513" s="12">
         <v>46169</v>
       </c>
@@ -5693,7 +5697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:2">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514" s="12">
         <v>46170</v>
       </c>
@@ -5701,7 +5705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:2">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515" s="12">
         <v>46171</v>
       </c>
@@ -5709,7 +5713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:2">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516" s="12">
         <v>46172</v>
       </c>
@@ -5717,7 +5721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:2">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517" s="12">
         <v>46173</v>
       </c>
@@ -5725,7 +5729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:2">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518" s="12">
         <v>46174</v>
       </c>
@@ -5733,7 +5737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:2">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519" s="12">
         <v>46175</v>
       </c>
@@ -5741,7 +5745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:2">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A520" s="12">
         <v>46176</v>
       </c>
@@ -5749,7 +5753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:2">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521" s="12">
         <v>46177</v>
       </c>
@@ -5757,7 +5761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:2">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522" s="12">
         <v>46178</v>
       </c>
@@ -5765,7 +5769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:2">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523" s="12">
         <v>46179</v>
       </c>
@@ -5773,7 +5777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:2">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524" s="12">
         <v>46180</v>
       </c>
@@ -5781,7 +5785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:2">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525" s="12">
         <v>46181</v>
       </c>
@@ -5789,7 +5793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:2">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526" s="12">
         <v>46182</v>
       </c>
@@ -5797,7 +5801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:2">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527" s="12">
         <v>46183</v>
       </c>
@@ -5805,7 +5809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:2">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528" s="12">
         <v>46184</v>
       </c>
@@ -5813,7 +5817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:2">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529" s="12">
         <v>46185</v>
       </c>
@@ -5821,7 +5825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:2">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530" s="12">
         <v>46186</v>
       </c>
@@ -5829,7 +5833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:2">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A531" s="12">
         <v>46187</v>
       </c>
@@ -5837,7 +5841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:2">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A532" s="12">
         <v>46188</v>
       </c>
@@ -5845,7 +5849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:2">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A533" s="12">
         <v>46189</v>
       </c>
@@ -5853,7 +5857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:2">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A534" s="12">
         <v>46190</v>
       </c>
@@ -5861,7 +5865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:2">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A535" s="12">
         <v>46191</v>
       </c>
@@ -5869,7 +5873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:2">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A536" s="12">
         <v>46192</v>
       </c>
@@ -5877,7 +5881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:2">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A537" s="12">
         <v>46193</v>
       </c>
@@ -5896,13 +5900,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -5916,7 +5920,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -5930,7 +5934,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>162</v>
       </c>
@@ -5944,7 +5948,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>169</v>
       </c>
@@ -5969,9 +5973,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -5985,7 +5989,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -5999,7 +6003,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>162</v>
       </c>
@@ -6013,7 +6017,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>169</v>
       </c>
@@ -6027,7 +6031,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>162</v>
       </c>
@@ -6041,7 +6045,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -6055,7 +6059,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>169</v>
       </c>
@@ -6069,7 +6073,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>162</v>
       </c>
@@ -6083,7 +6087,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>162</v>
       </c>
@@ -6097,7 +6101,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>169</v>
       </c>
@@ -6111,7 +6115,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -6125,7 +6129,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>162</v>
       </c>
@@ -6139,7 +6143,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>169</v>
       </c>
@@ -6164,9 +6168,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -6180,7 +6184,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -6194,7 +6198,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>162</v>
       </c>
@@ -6208,7 +6212,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>169</v>
       </c>
@@ -6222,7 +6226,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -6236,7 +6240,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>162</v>
       </c>
@@ -6250,7 +6254,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>162</v>
       </c>
@@ -6264,7 +6268,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>169</v>
       </c>
@@ -6278,7 +6282,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>169</v>
       </c>
@@ -6292,7 +6296,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>162</v>
       </c>
@@ -6306,7 +6310,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -6320,7 +6324,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>169</v>
       </c>
@@ -6334,7 +6338,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>169</v>
       </c>
@@ -6348,7 +6352,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>162</v>
       </c>
@@ -6362,7 +6366,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>162</v>
       </c>
@@ -6376,7 +6380,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>169</v>
       </c>
@@ -6390,7 +6394,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>169</v>
       </c>
@@ -6404,7 +6408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>162</v>
       </c>
@@ -6418,7 +6422,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>162</v>
       </c>
@@ -6432,7 +6436,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>169</v>
       </c>
@@ -6446,7 +6450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -6460,7 +6464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>162</v>
       </c>
@@ -6474,7 +6478,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>162</v>
       </c>
@@ -6499,9 +6503,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -6515,7 +6519,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -6529,7 +6533,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>162</v>
       </c>
@@ -6543,7 +6547,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>162</v>
       </c>
@@ -6557,7 +6561,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -6571,7 +6575,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>169</v>
       </c>
@@ -6585,7 +6589,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>169</v>
       </c>
@@ -6610,16 +6614,16 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -6651,7 +6655,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -6683,7 +6687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>169</v>
       </c>
@@ -6726,15 +6730,15 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -6748,7 +6752,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>164</v>
       </c>
@@ -6762,7 +6766,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>164</v>
       </c>
@@ -6776,7 +6780,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>164</v>
       </c>
@@ -6790,7 +6794,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>164</v>
       </c>
@@ -6804,7 +6808,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>164</v>
       </c>
@@ -6818,7 +6822,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>164</v>
       </c>
@@ -6832,7 +6836,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>164</v>
       </c>
@@ -6846,7 +6850,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>164</v>
       </c>
@@ -6860,7 +6864,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>164</v>
       </c>
@@ -6874,7 +6878,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>164</v>
       </c>
@@ -6888,7 +6892,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>164</v>
       </c>
@@ -6902,7 +6906,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>164</v>
       </c>
@@ -6916,7 +6920,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>164</v>
       </c>
@@ -6930,7 +6934,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>164</v>
       </c>
@@ -6944,7 +6948,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>164</v>
       </c>
@@ -6958,7 +6962,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>164</v>
       </c>
@@ -6972,7 +6976,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>164</v>
       </c>
@@ -6986,7 +6990,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>164</v>
       </c>
@@ -7000,7 +7004,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>164</v>
       </c>
@@ -7014,7 +7018,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>164</v>
       </c>
@@ -7028,7 +7032,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>164</v>
       </c>
@@ -7042,7 +7046,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>164</v>
       </c>
@@ -7056,7 +7060,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>164</v>
       </c>
@@ -7070,7 +7074,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>164</v>
       </c>
@@ -7084,7 +7088,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>164</v>
       </c>
@@ -7098,7 +7102,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>164</v>
       </c>
@@ -7112,7 +7116,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>164</v>
       </c>
@@ -7126,7 +7130,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>164</v>
       </c>
@@ -7140,7 +7144,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>164</v>
       </c>
@@ -7154,7 +7158,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>164</v>
       </c>
@@ -7168,7 +7172,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>164</v>
       </c>
@@ -7182,7 +7186,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>164</v>
       </c>
@@ -7196,7 +7200,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>164</v>
       </c>
@@ -7210,7 +7214,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>164</v>
       </c>
@@ -7224,7 +7228,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>164</v>
       </c>
@@ -7238,7 +7242,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>164</v>
       </c>
@@ -7252,7 +7256,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>164</v>
       </c>
@@ -7266,7 +7270,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>164</v>
       </c>
@@ -7280,7 +7284,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>164</v>
       </c>
@@ -7294,7 +7298,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>164</v>
       </c>
@@ -7308,7 +7312,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>164</v>
       </c>
@@ -7322,7 +7326,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>164</v>
       </c>
@@ -7336,7 +7340,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>164</v>
       </c>
@@ -7350,7 +7354,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>164</v>
       </c>
@@ -7364,7 +7368,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>164</v>
       </c>
@@ -7378,7 +7382,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>164</v>
       </c>
@@ -7392,7 +7396,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>164</v>
       </c>
@@ -7406,7 +7410,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>164</v>
       </c>
@@ -7431,14 +7435,14 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>122</v>
       </c>
@@ -7449,7 +7453,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -7460,7 +7464,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>169</v>
       </c>
@@ -7482,9 +7486,9 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -7501,7 +7505,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>212</v>
       </c>
@@ -7518,7 +7522,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -7535,7 +7539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>212</v>
       </c>
@@ -7552,7 +7556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>213</v>
       </c>
@@ -7580,28 +7584,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{498B42DD-2835-4AD3-BF47-63235B0B6DC7}">
   <dimension ref="B2:F117"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="57.28515625" customWidth="1"/>
-    <col min="6" max="6" width="70.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" customWidth="1"/>
+    <col min="5" max="5" width="57.33203125" customWidth="1"/>
+    <col min="6" max="6" width="70.33203125" customWidth="1"/>
+    <col min="7" max="7" width="19.88671875" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="2:6">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
         <v>32</v>
       </c>
@@ -7618,7 +7622,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="14.45" customHeight="1">
+    <row r="6" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>37</v>
       </c>
@@ -7632,7 +7636,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>37</v>
       </c>
@@ -7642,7 +7646,7 @@
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
@@ -7652,7 +7656,7 @@
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>37</v>
       </c>
@@ -7664,7 +7668,7 @@
       </c>
       <c r="F9" s="18"/>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
@@ -7676,7 +7680,7 @@
       </c>
       <c r="F10" s="18"/>
     </row>
-    <row r="11" spans="2:6">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>37</v>
       </c>
@@ -7688,7 +7692,7 @@
       </c>
       <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="2:6">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>48</v>
       </c>
@@ -7699,7 +7703,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>48</v>
       </c>
@@ -7708,7 +7712,7 @@
       </c>
       <c r="F13" s="18"/>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>48</v>
       </c>
@@ -7720,7 +7724,7 @@
       </c>
       <c r="F14" s="18"/>
     </row>
-    <row r="15" spans="2:6">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>48</v>
       </c>
@@ -7732,7 +7736,7 @@
       </c>
       <c r="F15" s="18"/>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>48</v>
       </c>
@@ -7744,7 +7748,7 @@
       </c>
       <c r="F16" s="18"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>48</v>
       </c>
@@ -7753,7 +7757,7 @@
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>58</v>
       </c>
@@ -7767,7 +7771,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>58</v>
       </c>
@@ -7781,7 +7785,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>62</v>
       </c>
@@ -7795,7 +7799,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>62</v>
       </c>
@@ -7805,7 +7809,7 @@
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
         <v>62</v>
       </c>
@@ -7815,7 +7819,7 @@
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
         <v>62</v>
       </c>
@@ -7825,7 +7829,7 @@
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
         <v>65</v>
       </c>
@@ -7839,7 +7843,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
         <v>68</v>
       </c>
@@ -7853,7 +7857,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>68</v>
       </c>
@@ -7863,7 +7867,7 @@
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
         <v>68</v>
       </c>
@@ -7873,7 +7877,7 @@
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
         <v>72</v>
       </c>
@@ -7887,7 +7891,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
         <v>72</v>
       </c>
@@ -7897,7 +7901,7 @@
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
         <v>72</v>
       </c>
@@ -7907,7 +7911,7 @@
       <c r="E30" s="17"/>
       <c r="F30" s="18"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
         <v>72</v>
       </c>
@@ -7917,7 +7921,7 @@
       <c r="E31" s="17"/>
       <c r="F31" s="18"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
         <v>76</v>
       </c>
@@ -7929,7 +7933,7 @@
       </c>
       <c r="F32" s="17"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
         <v>76</v>
       </c>
@@ -7939,7 +7943,7 @@
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="7" t="s">
         <v>80</v>
       </c>
@@ -7953,7 +7957,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
         <v>80</v>
       </c>
@@ -7963,7 +7967,7 @@
       <c r="E35" s="17"/>
       <c r="F35" s="18"/>
     </row>
-    <row r="36" spans="2:6">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
         <v>80</v>
       </c>
@@ -7973,7 +7977,7 @@
       <c r="E36" s="17"/>
       <c r="F36" s="18"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
         <v>80</v>
       </c>
@@ -7983,7 +7987,7 @@
       <c r="E37" s="17"/>
       <c r="F37" s="18"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
         <v>85</v>
       </c>
@@ -7994,7 +7998,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="7" t="s">
         <v>85</v>
       </c>
@@ -8003,7 +8007,7 @@
       </c>
       <c r="F39" s="17"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="7" t="s">
         <v>85</v>
       </c>
@@ -8015,7 +8019,7 @@
       </c>
       <c r="F40" s="17"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="7" t="s">
         <v>85</v>
       </c>
@@ -8027,7 +8031,7 @@
       </c>
       <c r="F41" s="17"/>
     </row>
-    <row r="42" spans="2:6">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="7" t="s">
         <v>85</v>
       </c>
@@ -8038,7 +8042,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
         <v>93</v>
       </c>
@@ -8052,7 +8056,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>93</v>
       </c>
@@ -8062,7 +8066,7 @@
       <c r="E44" s="17"/>
       <c r="F44" s="17"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="7" t="s">
         <v>93</v>
       </c>
@@ -8072,7 +8076,7 @@
       <c r="E45" s="17"/>
       <c r="F45" s="17"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
         <v>93</v>
       </c>
@@ -8082,7 +8086,7 @@
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
     </row>
-    <row r="47" spans="2:6">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="7" t="s">
         <v>98</v>
       </c>
@@ -8096,7 +8100,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
         <v>98</v>
       </c>
@@ -8106,7 +8110,7 @@
       <c r="E48" s="17"/>
       <c r="F48" s="17"/>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="7" t="s">
         <v>98</v>
       </c>
@@ -8116,7 +8120,7 @@
       <c r="E49" s="17"/>
       <c r="F49" s="17"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="7" t="s">
         <v>98</v>
       </c>
@@ -8126,7 +8130,7 @@
       <c r="E50" s="17"/>
       <c r="F50" s="17"/>
     </row>
-    <row r="51" spans="2:6" ht="26.45" customHeight="1">
+    <row r="51" spans="2:6" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="7" t="s">
         <v>102</v>
       </c>
@@ -8140,7 +8144,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="26.45" customHeight="1">
+    <row r="52" spans="2:6" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="7" t="s">
         <v>102</v>
       </c>
@@ -8150,7 +8154,7 @@
       <c r="E52" s="17"/>
       <c r="F52" s="17"/>
     </row>
-    <row r="53" spans="2:6" ht="26.45" customHeight="1">
+    <row r="53" spans="2:6" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
         <v>102</v>
       </c>
@@ -8160,7 +8164,7 @@
       <c r="E53" s="17"/>
       <c r="F53" s="17"/>
     </row>
-    <row r="54" spans="2:6" ht="26.45" customHeight="1">
+    <row r="54" spans="2:6" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
         <v>102</v>
       </c>
@@ -8170,7 +8174,7 @@
       <c r="E54" s="17"/>
       <c r="F54" s="17"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="7" t="s">
         <v>106</v>
       </c>
@@ -8178,7 +8182,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
         <v>106</v>
       </c>
@@ -8186,7 +8190,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
         <v>106</v>
       </c>
@@ -8194,7 +8198,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
         <v>106</v>
       </c>
@@ -8205,7 +8209,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="59" spans="2:6">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="7" t="s">
         <v>106</v>
       </c>
@@ -8216,7 +8220,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="2:6">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
         <v>106</v>
       </c>
@@ -8227,7 +8231,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B61" s="7" t="s">
         <v>106</v>
       </c>
@@ -8236,7 +8240,7 @@
       </c>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62" s="7" t="s">
         <v>106</v>
       </c>
@@ -8247,7 +8251,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="7" t="s">
         <v>106</v>
       </c>
@@ -8256,7 +8260,7 @@
       </c>
       <c r="E63" s="17"/>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="7" t="s">
         <v>106</v>
       </c>
@@ -8265,7 +8269,7 @@
       </c>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="2:5">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" s="7" t="s">
         <v>118</v>
       </c>
@@ -8276,7 +8280,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="2:5">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="7" t="s">
         <v>118</v>
       </c>
@@ -8285,7 +8289,7 @@
       </c>
       <c r="E66" s="17"/>
     </row>
-    <row r="67" spans="2:5">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B67" s="7" t="s">
         <v>118</v>
       </c>
@@ -8294,7 +8298,7 @@
       </c>
       <c r="E67" s="17"/>
     </row>
-    <row r="68" spans="2:5">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B68" s="7" t="s">
         <v>118</v>
       </c>
@@ -8303,7 +8307,7 @@
       </c>
       <c r="E68" s="17"/>
     </row>
-    <row r="69" spans="2:5">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
         <v>121</v>
       </c>
@@ -8311,7 +8315,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="70" spans="2:5">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B70" s="7" t="s">
         <v>121</v>
       </c>
@@ -8319,7 +8323,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="71" spans="2:5">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B71" s="7" t="s">
         <v>121</v>
       </c>
@@ -8327,7 +8331,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="72" spans="2:5">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B72" s="7" t="s">
         <v>125</v>
       </c>
@@ -8335,7 +8339,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="73" spans="2:5">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B73" s="7" t="s">
         <v>125</v>
       </c>
@@ -8343,7 +8347,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="2:5">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B74" s="7" t="s">
         <v>125</v>
       </c>
@@ -8354,7 +8358,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="75" spans="2:5">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75" s="7" t="s">
         <v>125</v>
       </c>
@@ -8365,7 +8369,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="76" spans="2:5">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76" s="7" t="s">
         <v>125</v>
       </c>
@@ -8376,7 +8380,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="77" spans="2:5">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77" s="7" t="s">
         <v>132</v>
       </c>
@@ -8384,7 +8388,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="78" spans="2:5">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B78" s="7" t="s">
         <v>132</v>
       </c>
@@ -8392,7 +8396,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="79" spans="2:5">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
         <v>132</v>
       </c>
@@ -8403,7 +8407,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="80" spans="2:5">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80" s="7" t="s">
         <v>135</v>
       </c>
@@ -8411,7 +8415,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="2:5">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="7" t="s">
         <v>135</v>
       </c>
@@ -8419,7 +8423,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="2:5">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
         <v>135</v>
       </c>
@@ -8430,7 +8434,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="83" spans="2:5">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" s="7" t="s">
         <v>138</v>
       </c>
@@ -8438,7 +8442,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="2:5">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" s="7" t="s">
         <v>138</v>
       </c>
@@ -8446,7 +8450,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="85" spans="2:5">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85" s="7" t="s">
         <v>138</v>
       </c>
@@ -8454,7 +8458,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="86" spans="2:5">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86" s="7" t="s">
         <v>138</v>
       </c>
@@ -8465,7 +8469,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="87" spans="2:5">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" s="7" t="s">
         <v>138</v>
       </c>
@@ -8473,7 +8477,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="88" spans="2:5">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" s="7" t="s">
         <v>138</v>
       </c>
@@ -8484,7 +8488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:5">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" s="7" t="s">
         <v>138</v>
       </c>
@@ -8495,7 +8499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:5">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" s="7" t="s">
         <v>141</v>
       </c>
@@ -8503,7 +8507,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="2:5">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91" s="7" t="s">
         <v>141</v>
       </c>
@@ -8511,7 +8515,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="92" spans="2:5">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" s="7" t="s">
         <v>141</v>
       </c>
@@ -8519,7 +8523,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="93" spans="2:5">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="7" t="s">
         <v>141</v>
       </c>
@@ -8527,7 +8531,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="2:5">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" s="7" t="s">
         <v>141</v>
       </c>
@@ -8535,7 +8539,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="95" spans="2:5">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="16" t="s">
         <v>141</v>
       </c>
@@ -8543,7 +8547,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="96" spans="2:5">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="7" t="s">
         <v>141</v>
       </c>
@@ -8551,7 +8555,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="97" spans="2:3">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B97" s="7" t="s">
         <v>147</v>
       </c>
@@ -8559,7 +8563,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="98" spans="2:3">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B98" s="7" t="s">
         <v>147</v>
       </c>
@@ -8567,7 +8571,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="2:3">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B99" s="7" t="s">
         <v>147</v>
       </c>
@@ -8575,7 +8579,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="100" spans="2:3">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B100" s="7" t="s">
         <v>147</v>
       </c>
@@ -8583,7 +8587,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="101" spans="2:3">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B101" s="7" t="s">
         <v>147</v>
       </c>
@@ -8591,7 +8595,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="102" spans="2:3">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B102" s="7" t="s">
         <v>149</v>
       </c>
@@ -8599,7 +8603,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="103" spans="2:3">
+    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B103" s="7" t="s">
         <v>149</v>
       </c>
@@ -8607,7 +8611,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="2:3">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B104" s="7" t="s">
         <v>149</v>
       </c>
@@ -8615,7 +8619,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="105" spans="2:3">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B105" s="7" t="s">
         <v>152</v>
       </c>
@@ -8623,7 +8627,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="2:3">
+    <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B106" s="7" t="s">
         <v>152</v>
       </c>
@@ -8631,7 +8635,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="107" spans="2:3">
+    <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B107" s="7" t="s">
         <v>152</v>
       </c>
@@ -8639,7 +8643,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="108" spans="2:3">
+    <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B108" s="7" t="s">
         <v>152</v>
       </c>
@@ -8647,7 +8651,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="2:3">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109" s="7" t="s">
         <v>155</v>
       </c>
@@ -8655,7 +8659,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="110" spans="2:3">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B110" s="7" t="s">
         <v>155</v>
       </c>
@@ -8663,7 +8667,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="111" spans="2:3">
+    <row r="111" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B111" s="7" t="s">
         <v>155</v>
       </c>
@@ -8671,7 +8675,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="112" spans="2:3">
+    <row r="112" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B112" s="7" t="s">
         <v>155</v>
       </c>
@@ -8679,7 +8683,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="113" spans="2:3">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B113" s="7" t="s">
         <v>155</v>
       </c>
@@ -8687,7 +8691,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="114" spans="2:3">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114" s="7" t="s">
         <v>159</v>
       </c>
@@ -8695,7 +8699,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="115" spans="2:3">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B115" s="7" t="s">
         <v>159</v>
       </c>
@@ -8703,7 +8707,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="116" spans="2:3">
+    <row r="116" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B116" s="7" t="s">
         <v>159</v>
       </c>
@@ -8711,7 +8715,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="117" spans="2:3">
+    <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B117" s="7" t="s">
         <v>159</v>
       </c>
@@ -8757,9 +8761,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -8770,7 +8774,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>164</v>
       </c>
@@ -8781,7 +8785,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>164</v>
       </c>
@@ -8803,9 +8807,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -8816,7 +8820,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -8827,7 +8831,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>169</v>
       </c>
@@ -8849,9 +8853,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -8874,7 +8878,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -8897,7 +8901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>162</v>
       </c>
@@ -8920,7 +8924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>169</v>
       </c>
@@ -8954,12 +8958,12 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="8.85546875" style="3"/>
+    <col min="7" max="7" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -8982,7 +8986,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>164</v>
       </c>
@@ -9005,7 +9009,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>164</v>
       </c>
@@ -9028,7 +9032,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>163</v>
       </c>
@@ -9051,7 +9055,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -9085,14 +9089,14 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="8.85546875" style="3"/>
-    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="8.88671875" style="3"/>
+    <col min="5" max="5" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -9112,7 +9116,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -9132,7 +9136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>169</v>
       </c>
@@ -9163,16 +9167,16 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
@@ -9189,7 +9193,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>166</v>
       </c>
@@ -9206,7 +9210,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>166</v>
       </c>
@@ -9223,7 +9227,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>189</v>
       </c>
@@ -9240,7 +9244,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>189</v>
       </c>
@@ -9257,7 +9261,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>190</v>
       </c>
@@ -9274,7 +9278,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>190</v>
       </c>
@@ -9291,7 +9295,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>191</v>
       </c>
@@ -9308,7 +9312,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>191</v>
       </c>
@@ -9325,7 +9329,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>192</v>
       </c>
@@ -9342,7 +9346,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>192</v>
       </c>
@@ -9359,7 +9363,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>193</v>
       </c>
@@ -9376,7 +9380,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>193</v>
       </c>
@@ -9393,7 +9397,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>194</v>
       </c>
@@ -9410,7 +9414,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>194</v>
       </c>
@@ -9438,9 +9442,9 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -9460,7 +9464,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>223</v>
       </c>
@@ -9491,9 +9495,9 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>142</v>
       </c>
@@ -9510,7 +9514,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>215</v>
       </c>
@@ -9527,7 +9531,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>217</v>
       </c>
@@ -9544,7 +9548,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>218</v>
       </c>
@@ -9572,9 +9576,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
@@ -9591,7 +9595,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>166</v>
       </c>
@@ -9608,7 +9612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>166</v>
       </c>
@@ -9625,7 +9629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>189</v>
       </c>
@@ -9642,7 +9646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>189</v>
       </c>
@@ -9659,7 +9663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>190</v>
       </c>
@@ -9676,7 +9680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>190</v>
       </c>
@@ -9693,7 +9697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>191</v>
       </c>
@@ -9710,7 +9714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>191</v>
       </c>
@@ -9727,7 +9731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>192</v>
       </c>
@@ -9744,7 +9748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>192</v>
       </c>
@@ -9761,7 +9765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>193</v>
       </c>
@@ -9778,7 +9782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>193</v>
       </c>
@@ -9795,7 +9799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>194</v>
       </c>
@@ -9812,7 +9816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>194</v>
       </c>
@@ -9829,7 +9833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>166</v>
       </c>
@@ -9846,7 +9850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>189</v>
       </c>
@@ -9863,7 +9867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>190</v>
       </c>
@@ -9880,7 +9884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>191</v>
       </c>
@@ -9897,7 +9901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>192</v>
       </c>
@@ -9914,7 +9918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>193</v>
       </c>
@@ -9931,7 +9935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>194</v>
       </c>
@@ -9948,7 +9952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>166</v>
       </c>
@@ -9965,7 +9969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>189</v>
       </c>
@@ -9982,7 +9986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>190</v>
       </c>
@@ -9999,7 +10003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>191</v>
       </c>
@@ -10016,7 +10020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>192</v>
       </c>
@@ -10033,7 +10037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>193</v>
       </c>
@@ -10050,7 +10054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>194</v>
       </c>
@@ -10067,7 +10071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>166</v>
       </c>
@@ -10084,7 +10088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>189</v>
       </c>
@@ -10101,7 +10105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>190</v>
       </c>
@@ -10118,7 +10122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>191</v>
       </c>
@@ -10135,7 +10139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>192</v>
       </c>
@@ -10152,7 +10156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>193</v>
       </c>
@@ -10169,7 +10173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>194</v>
       </c>
@@ -10186,7 +10190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>166</v>
       </c>
@@ -10203,7 +10207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>189</v>
       </c>
@@ -10220,7 +10224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>190</v>
       </c>
@@ -10237,7 +10241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>191</v>
       </c>
@@ -10254,7 +10258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>192</v>
       </c>
@@ -10271,7 +10275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>193</v>
       </c>
@@ -10288,7 +10292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>194</v>
       </c>
@@ -10305,7 +10309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>166</v>
       </c>
@@ -10322,7 +10326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>189</v>
       </c>
@@ -10339,7 +10343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>190</v>
       </c>
@@ -10356,7 +10360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>191</v>
       </c>
@@ -10373,7 +10377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>192</v>
       </c>
@@ -10390,7 +10394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>193</v>
       </c>
@@ -10407,7 +10411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>194</v>
       </c>
@@ -10435,16 +10439,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -10464,7 +10468,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -10484,7 +10488,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>162</v>
       </c>
@@ -10504,7 +10508,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>169</v>
       </c>
@@ -10535,13 +10539,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -10555,7 +10559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>164</v>
       </c>
@@ -10569,7 +10573,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>163</v>
       </c>
@@ -10583,7 +10587,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>168</v>
       </c>
@@ -10608,9 +10612,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -10630,7 +10634,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>164</v>
       </c>
@@ -10650,7 +10654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>164</v>
       </c>
@@ -10670,7 +10674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>163</v>
       </c>
@@ -10690,7 +10694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -10721,14 +10725,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601DF4DB-1750-4EC9-BAF8-AE268C07143E}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>42</v>
       </c>
@@ -10744,13 +10748,13 @@
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -10758,7 +10762,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>170</v>
       </c>
@@ -10766,7 +10770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>171</v>
       </c>
@@ -10774,7 +10778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>172</v>
       </c>
@@ -10782,7 +10786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>173</v>
       </c>
@@ -10790,7 +10794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>174</v>
       </c>
@@ -10798,7 +10802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>175</v>
       </c>
@@ -10806,7 +10810,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>176</v>
       </c>
@@ -10814,7 +10818,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>177</v>
       </c>
@@ -10822,7 +10826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>178</v>
       </c>
@@ -10830,7 +10834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>179</v>
       </c>
@@ -10838,7 +10842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>180</v>
       </c>
@@ -10846,7 +10850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>181</v>
       </c>
@@ -10854,7 +10858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>182</v>
       </c>
@@ -10862,7 +10866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>183</v>
       </c>
@@ -10870,7 +10874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>184</v>
       </c>
@@ -10878,7 +10882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>185</v>
       </c>
@@ -10886,7 +10890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>186</v>
       </c>
@@ -10899,18 +10903,15 @@
   <headerFooter>
     <oddHeader>&amp;R&amp;"Calibri"&amp;10&amp;K000000 Business Use&amp;1#_x000D_</oddHeader>
   </headerFooter>
-  <customProperties>
-    <customPr name="IbpWorksheetKeyString_GUID" r:id="rId1"/>
-  </customProperties>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -10921,7 +10922,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -10932,7 +10933,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>162</v>
       </c>
@@ -10943,7 +10944,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>162</v>
       </c>
@@ -10954,7 +10955,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -10965,7 +10966,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>169</v>
       </c>
@@ -10976,7 +10977,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>169</v>
       </c>
@@ -10998,9 +10999,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
@@ -11014,7 +11015,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -11028,7 +11029,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -11042,7 +11043,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -11056,7 +11057,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -11070,7 +11071,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
@@ -11084,7 +11085,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -11098,7 +11099,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -11112,7 +11113,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -11126,7 +11127,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -11140,7 +11141,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
@@ -11154,7 +11155,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>4</v>
       </c>
@@ -11168,7 +11169,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>4</v>
       </c>
@@ -11182,7 +11183,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>5</v>
       </c>
@@ -11196,7 +11197,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>5</v>
       </c>
@@ -11210,7 +11211,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>5</v>
       </c>
@@ -11224,7 +11225,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>6</v>
       </c>
@@ -11238,7 +11239,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>6</v>
       </c>
@@ -11252,7 +11253,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>6</v>
       </c>
@@ -11266,7 +11267,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>7</v>
       </c>
@@ -11280,7 +11281,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>7</v>
       </c>
@@ -11294,7 +11295,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>7</v>
       </c>
@@ -11308,7 +11309,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>8</v>
       </c>
@@ -11322,7 +11323,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>8</v>
       </c>
@@ -11336,7 +11337,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>8</v>
       </c>
@@ -11350,7 +11351,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>9</v>
       </c>
@@ -11364,7 +11365,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>9</v>
       </c>
@@ -11378,7 +11379,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>9</v>
       </c>
@@ -11392,7 +11393,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>10</v>
       </c>
@@ -11406,7 +11407,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>10</v>
       </c>
@@ -11420,7 +11421,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>10</v>
       </c>
@@ -11434,7 +11435,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>11</v>
       </c>
@@ -11448,7 +11449,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>11</v>
       </c>
@@ -11462,7 +11463,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>11</v>
       </c>
@@ -11476,7 +11477,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>12</v>
       </c>
@@ -11490,7 +11491,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>12</v>
       </c>
@@ -11504,7 +11505,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>12</v>
       </c>
